--- a/artfynd/A 29016-2025 artfynd.xlsx
+++ b/artfynd/A 29016-2025 artfynd.xlsx
@@ -2478,7 +2478,7 @@
         <v>127006757</v>
       </c>
       <c r="B17" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 29016-2025 artfynd.xlsx
+++ b/artfynd/A 29016-2025 artfynd.xlsx
@@ -2478,7 +2478,7 @@
         <v>127006757</v>
       </c>
       <c r="B17" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 29016-2025 artfynd.xlsx
+++ b/artfynd/A 29016-2025 artfynd.xlsx
@@ -2478,7 +2478,7 @@
         <v>127006757</v>
       </c>
       <c r="B17" t="n">
-        <v>57660</v>
+        <v>57654</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 29016-2025 artfynd.xlsx
+++ b/artfynd/A 29016-2025 artfynd.xlsx
@@ -2478,7 +2478,7 @@
         <v>127006757</v>
       </c>
       <c r="B17" t="n">
-        <v>57654</v>
+        <v>57660</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
